--- a/data/merged/2026-09-09/MERGED_US_Robot-Vacuum_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_US_Robot-Vacuum_2026-09-09.xlsx
@@ -7306,94 +7306,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7719,7 +7631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -18494,125 +18406,115 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0C7C7PLLG</t>
+          <t>B0HBQJ9M76</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>eufy</t>
+          <t>iMartine</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/eufy/page/B02CB877-324C-4130-B1A3-41E418F2C467?lp_asin=B0C7C7PLLG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/stores/iMartine/page/654ED1F3-3554-4D70-BE13-648A97EF447C?lp_asin=B0HBQJ9M76&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>eufy RoboVac Hard Floor Cleaning Solution (2 Bottles), Dilution Ratio 1:200, 473 ml, Floor Cleaner, Plant-Based,Compatible wi</t>
+          <t>iMartine Robot Vacuum and Mop Combo, Strong Suction, 2-in-1 Dust Box and Water Tank, Works with Alexa/Google Assistant, Long</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0C7C7PLLG?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HBQJ9M76?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/511jqutQR2L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71SXkH+kJRL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0C7C7PLLG</t>
+          <t>B0HBQJ9M76</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>Industrial &amp; Scientific:Janitorial &amp; Sanitation Supplies:Vacuums &amp; Floor Cleaning Machines:Vacuums:Robotic Vacuums</t>
+          <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
       <c r="N46" s="14" t="inlineStr">
         <is>
-          <t>Industrial &amp; Scientific</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="O46" s="15">
-        <v>1678</v>
+        <v>15094</v>
       </c>
       <c r="P46" s="15">
-        <v>521</v>
+        <v>1897976</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.24</v>
+        <v>0.99</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
-          <t>Commercial Indoor Robotic Vacuums
-Robotic Vacuums</t>
+          <t>Robotic Vacuums</t>
         </is>
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>4
-17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>2542</v>
-      </c>
-      <c r="U46" s="16">
-        <v>-0.23</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="U46" s="16"/>
       <c r="V46" s="15">
-        <v>57170</v>
-      </c>
-      <c r="W46" s="15" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="X46" s="15">
-        <v>56200</v>
-      </c>
+        <v>29819</v>
+      </c>
+      <c r="W46" s="15"/>
+      <c r="X46" s="15"/>
       <c r="Y46" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z46" s="20">
-        <v>22.49</v>
+        <v>114.69</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="19">
-        <v>1499</v>
+        <v>4810</v>
       </c>
       <c r="AE46" s="15">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.0087</v>
+        <v>0</v>
       </c>
       <c r="AH46" s="20">
-        <v>6.31</v>
+        <v>9.33</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>1166</v>
+        <v>25</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
@@ -18630,7 +18532,7 @@
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Anker EufyHome</t>
+          <t>Tchenxmian</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
@@ -18640,85 +18542,77 @@
       </c>
       <c r="AU46" s="13" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV46" s="14" t="inlineStr">
         <is>
-          <t>WA 98004 US</t>
+          <t>KOWLOON HONG KONG 999077 HK</t>
         </is>
       </c>
       <c r="AW46" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U62USFOR8NN3</t>
+          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SWRS4GCWE28K</t>
         </is>
       </c>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
-      <c r="BB46" s="13"/>
+      <c r="BB46" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BC46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD46" s="13"/>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>2.31 pounds</t>
+          <t>7.69 pounds</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>1.05 kg</t>
+          <t>3.49 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>8.8 x 4.4 x 2 inches</t>
+          <t>11.8 x 11.8 x 2.9 inches</t>
         </is>
       </c>
       <c r="BM46" s="23" t="inlineStr">
         <is>
-          <t>22.35 x 11.18 x 5.08 cm</t>
+          <t>29.97 x 29.97 x 7.37 cm</t>
         </is>
       </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>2.38 pounds</t>
+          <t>7.74 pounds</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>1.08 kg</t>
+          <t>3.51 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>8.9 x 4.5 x 4 inches</t>
+          <t>16 x 13.7 x 5.2 inches</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>22.61 x 11.43 x 10.16 cm</t>
+          <t>40.64 x 34.80 x 13.21 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
@@ -18734,131 +18628,129 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0BCF8N3B4</t>
+          <t>B07BRVNXZW</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS</t>
+          <t>roborock</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/ECOVACS/page/E74F14EC-79FC-433B-8BB9-DA6190E35D28?lp_asin=B0BCF8N3B4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B07BRVNXZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS Multi-Surface Floor Cleaning Solution, Compatible with DEEBOT X11 OMNI Cyclone / X9 PRO OMNI / T80 OMNI / T50 PRO OMN</t>
+          <t>roborock Side Brushes Replacement (2 Pieces) for S8 Pro Ultra, S7 Max Ultra, Q Revo, Series of S7 MaxV/S7/Q7Max/Q8 Max/S8/Q7/</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0BCF8N3B4?psc=1</t>
+          <t>https://www.amazon.com/dp/B07BRVNXZW?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51OKmAG4ODL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/21Oz8FY385L._SX600_SY600_CR,0,0,600,600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0BCF8N3B4</t>
+          <t>B07BRVNXZW</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
         <is>
-          <t>Industrial &amp; Scientific:Janitorial &amp; Sanitation Supplies:Vacuums &amp; Floor Cleaning Machines:Vacuums:Robotic Vacuums</t>
+          <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
       <c r="N47" s="14" t="inlineStr">
         <is>
-          <t>Industrial &amp; Scientific</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="O47" s="15">
-        <v>2088</v>
+        <v>31987</v>
       </c>
       <c r="P47" s="15">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
-          <t>Commercial Indoor Robotic Vacuums
-Robotic Vacuums</t>
+          <t>Robotic Vacuums</t>
         </is>
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>5
-21</t>
+          <t>39</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>2262</v>
+        <v>1031</v>
       </c>
       <c r="U47" s="16">
-        <v>-0.01</v>
+        <v>0.34</v>
       </c>
       <c r="V47" s="15">
-        <v>56527</v>
+        <v>16486</v>
       </c>
       <c r="W47" s="15" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X47" s="15">
-        <v>49600</v>
+        <v>1599</v>
       </c>
       <c r="Y47" s="19">
         <v>2</v>
       </c>
       <c r="Z47" s="20">
-        <v>24.99</v>
+        <v>15.99</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="2">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="AD47" s="19">
-        <v>1204</v>
+        <v>860</v>
       </c>
       <c r="AE47" s="15">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AF47" s="21">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AG47" s="22">
-        <v>0.0111</v>
+        <v>0.010700000000000001</v>
       </c>
       <c r="AH47" s="20">
-        <v>6.48</v>
+        <v>4.09</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2023-02-17</t>
+          <t>2018-05-08</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>1299</v>
+        <v>3046</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
@@ -18872,17 +18764,29 @@
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Roborock Technology Co. Ltd</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU47" s="13"/>
-      <c r="AV47" s="14"/>
-      <c r="AW47" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU47" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV47" s="14" t="inlineStr">
+        <is>
+          <t>SHEUNG WAN HK 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW47" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH</t>
+        </is>
+      </c>
       <c r="AX47" s="13"/>
       <c r="AY47" s="13" t="inlineStr">
         <is>
@@ -18909,42 +18813,42 @@
       </c>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>2.69 pounds</t>
+          <t>1.8 ounces</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>1.22 kg</t>
+          <t>51.03 g</t>
         </is>
       </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>3.5 x 3.5 x 9.7 inches</t>
+          <t>2.36"L x 2.36"W x 0.39"H</t>
         </is>
       </c>
       <c r="BM47" s="23" t="inlineStr">
         <is>
-          <t>8.89 x 8.89 x 24.64 cm</t>
+          <t>5.99 x 5.99 x 0.99 cm</t>
         </is>
       </c>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>2.62 pounds</t>
+          <t>0.11 pounds</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>1.19 kg</t>
+          <t>49.90 g</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>9.7 x 3.5 x 3.5 inches</t>
+          <t>4.6 x 4.6 x 2 inches</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>24.64 x 8.89 x 8.89 cm</t>
+          <t>11.68 x 11.68 x 5.08 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
@@ -18960,40 +18864,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0HBQJ9M76</t>
+          <t>B0GQ2W9M3M</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>iMartine</t>
+          <t>XIEBro</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/iMartine/page/654ED1F3-3554-4D70-BE13-648A97EF447C?lp_asin=B0HBQJ9M76&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/stores/XIEBroRobotVacuumandMop/page/63D629A5-9469-4862-85F6-A208E9F2C951?lp_asin=B0GQ2W9M3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>iMartine Robot Vacuum and Mop Combo, Strong Suction, 2-in-1 Dust Box and Water Tank, Works with Alexa/Google Assistant, Long</t>
+          <t>XIEBro Robot Vacuum and Mop, 6500Pa Suction, 2 in 1 Robotic Vacuum with Gyro Inertial Navigation, 200 Min Runtime, App/Remote</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0HBQJ9M76?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GQ2W9M3M?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71SXkH+kJRL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0HBQJ9M76</t>
+          <t>B0GQ2W9M3M</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -19007,13 +18911,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>15094</v>
+        <v>26560</v>
       </c>
       <c r="P48" s="15">
-        <v>1897976</v>
+        <v>1255807</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -19022,53 +18926,59 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>260</v>
+        <v>126</v>
       </c>
       <c r="U48" s="16"/>
       <c r="V48" s="15">
-        <v>29819</v>
-      </c>
-      <c r="W48" s="15"/>
-      <c r="X48" s="15"/>
+        <v>15119</v>
+      </c>
+      <c r="W48" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X48" s="15">
+        <v>37685</v>
+      </c>
       <c r="Y48" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>114.69</v>
+        <v>119.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="19">
-        <v>4810</v>
+        <v>18</v>
       </c>
       <c r="AE48" s="15">
         <v>0</v>
       </c>
       <c r="AF48" s="21">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AG48" s="22">
         <v>0</v>
       </c>
       <c r="AH48" s="20">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
@@ -19082,11 +18992,11 @@
         <v>10</v>
       </c>
       <c r="AR48" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Tchenxmian</t>
+          <t>zchenymei</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
@@ -19101,72 +19011,80 @@
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>KOWLOON HONG KONG 999077 HK</t>
+          <t>KOWLOON HONGKONG 999077 HK</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SWRS4GCWE28K</t>
+          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P2R2P57KGCPN</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
-      <c r="AY48" s="13"/>
+      <c r="AY48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
-      <c r="BB48" s="13" t="inlineStr">
+      <c r="BB48" s="13"/>
+      <c r="BC48" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BC48" s="13" t="inlineStr">
+      <c r="BD48" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD48" s="13"/>
       <c r="BE48" s="13"/>
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
-      <c r="BI48" s="23"/>
+      <c r="BI48" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>7.69 pounds</t>
+          <t>7.04 pounds</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>3.49 kg</t>
+          <t>3.19 kg</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>11.8 x 11.8 x 2.9 inches</t>
+          <t>11.8 x 11.8 x 3 inches</t>
         </is>
       </c>
       <c r="BM48" s="23" t="inlineStr">
         <is>
-          <t>29.97 x 29.97 x 7.37 cm</t>
+          <t>29.97 x 29.97 x 7.62 cm</t>
         </is>
       </c>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>7.74 pounds</t>
+          <t>7.05 pounds</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>3.51 kg</t>
+          <t>3.20 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>16 x 13.7 x 5.2 inches</t>
+          <t>16.5 x 13 x 4.2 inches</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>40.64 x 34.80 x 13.21 cm</t>
+          <t>41.91 x 33.02 x 10.67 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
@@ -19182,40 +19100,40 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B07BRVNXZW</t>
+          <t>B0HFJJ589K</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>roborock</t>
+          <t>wrydao</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B07BRVNXZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0HFJJ589K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>roborock Side Brushes Replacement (2 Pieces) for S8 Pro Ultra, S7 Max Ultra, Q Revo, Series of S7 MaxV/S7/Q7Max/Q8 Max/S8/Q7/</t>
+          <t>Robot Vacuum and Mop with Mapping: 6000Pa LIDAR Navigation Self Emptying Robotic Vacuum,Alexa/APP Control 3-in-1 Robot Vacuum</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B07BRVNXZW?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HFJJ589K?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/21Oz8FY385L._SX600_SY600_CR,0,0,600,600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71cb8CCFNBL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B07BRVNXZW</t>
+          <t>B0HFJJ589K</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -19229,13 +19147,11 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>31987</v>
-      </c>
-      <c r="P49" s="15">
-        <v>720</v>
-      </c>
+        <v>36267</v>
+      </c>
+      <c r="P49" s="15"/>
       <c r="Q49" s="16">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -19244,63 +19160,53 @@
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>1031</v>
-      </c>
-      <c r="U49" s="16">
-        <v>0.34</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="U49" s="16"/>
       <c r="V49" s="15">
-        <v>16486</v>
-      </c>
-      <c r="W49" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X49" s="15">
-        <v>1599</v>
-      </c>
+        <v>11520</v>
+      </c>
+      <c r="W49" s="15"/>
+      <c r="X49" s="15"/>
       <c r="Y49" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="20">
-        <v>15.99</v>
+        <v>239.99</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
-      <c r="AC49" s="2">
+      <c r="AC49" s="2"/>
+      <c r="AD49" s="19">
+        <v>43</v>
+      </c>
+      <c r="AE49" s="15">
         <v>23</v>
       </c>
-      <c r="AD49" s="19">
-        <v>860</v>
-      </c>
-      <c r="AE49" s="15">
-        <v>11</v>
-      </c>
       <c r="AF49" s="21">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.010700000000000001</v>
+        <v>0.4792</v>
       </c>
       <c r="AH49" s="20">
-        <v>4.09</v>
+        <v>18</v>
       </c>
       <c r="AI49" s="16">
-        <v>0.59</v>
+        <v>0.78</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2018-05-08</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>3046</v>
+        <v>15</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
@@ -19314,11 +19220,11 @@
         <v>10</v>
       </c>
       <c r="AR49" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>Roborock Technology Co. Ltd</t>
+          <t>HanHaoDongMoYuan20J-US</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
@@ -19328,17 +19234,17 @@
       </c>
       <c r="AU49" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>SHEUNG WAN HK 999077 HK</t>
+          <t>西安市 陕西 710000 CN</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH</t>
+          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18INPDUBKKX96</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
@@ -19367,505 +19273,45 @@
       </c>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>1.8 ounces</t>
+          <t>12.12 pounds</t>
         </is>
       </c>
       <c r="BK49" s="23" t="inlineStr">
         <is>
-          <t>51.03 g</t>
+          <t>5.50 kg</t>
         </is>
       </c>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>2.36"L x 2.36"W x 0.39"H</t>
+          <t>12.5 x 12.5 x 3.5 inches</t>
         </is>
       </c>
       <c r="BM49" s="23" t="inlineStr">
         <is>
-          <t>5.99 x 5.99 x 0.99 cm</t>
+          <t>31.75 x 31.75 x 8.89 cm</t>
         </is>
       </c>
       <c r="BN49" s="23" t="inlineStr">
         <is>
-          <t>0.11 pounds</t>
+          <t>12.14 pounds</t>
         </is>
       </c>
       <c r="BO49" s="23" t="inlineStr">
         <is>
-          <t>49.90 g</t>
+          <t>5.51 kg</t>
         </is>
       </c>
       <c r="BP49" s="23" t="inlineStr">
         <is>
-          <t>4.6 x 4.6 x 2 inches</t>
+          <t>14.9 x 14 x 12.7 inches</t>
         </is>
       </c>
       <c r="BQ49" s="23" t="inlineStr">
         <is>
-          <t>11.68 x 11.68 x 5.08 cm</t>
+          <t>37.85 x 35.56 x 32.26 cm</t>
         </is>
       </c>
       <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>大号标准尺寸</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0GQ2W9M3M</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>XIEBro</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/stores/XIEBroRobotVacuumandMop/page/63D629A5-9469-4862-85F6-A208E9F2C951?lp_asin=B0GQ2W9M3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>XIEBro Robot Vacuum and Mop, 6500Pa Suction, 2 in 1 Robotic Vacuum with Gyro Inertial Navigation, 200 Min Runtime, App/Remote</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0GQ2W9M3M?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0GQ2W9M3M</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>26560</v>
-      </c>
-      <c r="P50" s="15">
-        <v>1255807</v>
-      </c>
-      <c r="Q50" s="16">
-        <v>0.98</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>126</v>
-      </c>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15">
-        <v>15119</v>
-      </c>
-      <c r="W50" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X50" s="15">
-        <v>37685</v>
-      </c>
-      <c r="Y50" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>119.99</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="19">
-        <v>18</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="21">
-        <v>4.9</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="20">
-        <v>9</v>
-      </c>
-      <c r="AI50" s="16">
-        <v>0.78</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>137</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR50" s="19">
-        <v>3</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>zchenymei</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU50" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV50" s="14" t="inlineStr">
-        <is>
-          <t>KOWLOON HONGKONG 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW50" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P2R2P57KGCPN</t>
-        </is>
-      </c>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>7.04 pounds</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>3.19 kg</t>
-        </is>
-      </c>
-      <c r="BL50" s="23" t="inlineStr">
-        <is>
-          <t>11.8 x 11.8 x 3 inches</t>
-        </is>
-      </c>
-      <c r="BM50" s="23" t="inlineStr">
-        <is>
-          <t>29.97 x 29.97 x 7.62 cm</t>
-        </is>
-      </c>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>7.05 pounds</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>3.20 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>16.5 x 13 x 4.2 inches</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>41.91 x 33.02 x 10.67 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>大号标准尺寸</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HFJJ589K</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>wrydao</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0HFJJ589K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Robot Vacuum and Mop with Mapping: 6000Pa LIDAR Navigation Self Emptying Robotic Vacuum,Alexa/APP Control 3-in-1 Robot Vacuum</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0HFJJ589K?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71cb8CCFNBL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HFJJ589K</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>36267</v>
-      </c>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16">
-        <v>0</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>48</v>
-      </c>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15">
-        <v>11520</v>
-      </c>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>239.99</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>43</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>23</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.9</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0.4792</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>18</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.78</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>15</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>HanHaoDongMoYuan20J-US</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV51" s="14" t="inlineStr">
-        <is>
-          <t>西安市 陕西 710000 CN</t>
-        </is>
-      </c>
-      <c r="AW51" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18INPDUBKKX96</t>
-        </is>
-      </c>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>12.12 pounds</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>5.50 kg</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>12.5 x 12.5 x 3.5 inches</t>
-        </is>
-      </c>
-      <c r="BM51" s="23" t="inlineStr">
-        <is>
-          <t>31.75 x 31.75 x 8.89 cm</t>
-        </is>
-      </c>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>12.14 pounds</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>5.51 kg</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>14.9 x 14 x 12.7 inches</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>37.85 x 35.56 x 32.26 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
         <is>
           <t>小号大件</t>
         </is>
@@ -20212,55 +19658,40 @@
     <hyperlink ref="M45" r:id="rId335" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N45" r:id="rId336"/>
     <hyperlink ref="AW45" r:id="rId337" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2HEK92N58O38H"/>
-    <hyperlink ref="C46" r:id="rId338" tooltip="https://www.amazon.com/dp/B0C7C7PLLG"/>
-    <hyperlink ref="G46" r:id="rId339" tooltip="https://www.amazon.com/stores/eufy/page/B02CB877-324C-4130-B1A3-41E418F2C467?lp_asin=B0C7C7PLLG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId340" tooltip="https://www.amazon.com/dp/B0C7C7PLLG?psc=1"/>
-    <hyperlink ref="K46" r:id="rId341" tooltip="https://images-na.ssl-images-amazon.com/images/I/511jqutQR2L._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId342" tooltip="https://www.amazon.com/dp/B0C7C7PLLG"/>
-    <hyperlink ref="M46" r:id="rId343" tooltip="https://www.amazon.com/b?node=3256980011"/>
+    <hyperlink ref="C46" r:id="rId338" tooltip="https://www.amazon.com/dp/B0HBQJ9M76"/>
+    <hyperlink ref="G46" r:id="rId339" tooltip="https://www.amazon.com/stores/iMartine/page/654ED1F3-3554-4D70-BE13-648A97EF447C?lp_asin=B0HBQJ9M76&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J46" r:id="rId340" tooltip="https://www.amazon.com/dp/B0HBQJ9M76?psc=1"/>
+    <hyperlink ref="K46" r:id="rId341" tooltip="https://images-na.ssl-images-amazon.com/images/I/71SXkH+kJRL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId342" tooltip="https://www.amazon.com/dp/B0HBQJ9M76"/>
+    <hyperlink ref="M46" r:id="rId343" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N46" r:id="rId344"/>
-    <hyperlink ref="AW46" r:id="rId345" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U62USFOR8NN3"/>
-    <hyperlink ref="C47" r:id="rId346" tooltip="https://www.amazon.com/dp/B0BCF8N3B4"/>
-    <hyperlink ref="G47" r:id="rId347" tooltip="https://www.amazon.com/stores/ECOVACS/page/E74F14EC-79FC-433B-8BB9-DA6190E35D28?lp_asin=B0BCF8N3B4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId348" tooltip="https://www.amazon.com/dp/B0BCF8N3B4?psc=1"/>
-    <hyperlink ref="K47" r:id="rId349" tooltip="https://images-na.ssl-images-amazon.com/images/I/51OKmAG4ODL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId350" tooltip="https://www.amazon.com/dp/B0BCF8N3B4"/>
-    <hyperlink ref="M47" r:id="rId351" tooltip="https://www.amazon.com/b?node=3256980011"/>
+    <hyperlink ref="AW46" r:id="rId345" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SWRS4GCWE28K"/>
+    <hyperlink ref="C47" r:id="rId346" tooltip="https://www.amazon.com/dp/B07BRVNXZW"/>
+    <hyperlink ref="G47" r:id="rId347" tooltip="https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B07BRVNXZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J47" r:id="rId348" tooltip="https://www.amazon.com/dp/B07BRVNXZW?psc=1"/>
+    <hyperlink ref="K47" r:id="rId349" tooltip="https://m.media-amazon.com/images/I/21Oz8FY385L._SX600_SY600_CR,0,0,600,600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId350" tooltip="https://www.amazon.com/dp/B07BRVNXZW"/>
+    <hyperlink ref="M47" r:id="rId351" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N47" r:id="rId352"/>
-    <hyperlink ref="C48" r:id="rId353" tooltip="https://www.amazon.com/dp/B0HBQJ9M76"/>
-    <hyperlink ref="G48" r:id="rId354" tooltip="https://www.amazon.com/stores/iMartine/page/654ED1F3-3554-4D70-BE13-648A97EF447C?lp_asin=B0HBQJ9M76&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId355" tooltip="https://www.amazon.com/dp/B0HBQJ9M76?psc=1"/>
-    <hyperlink ref="K48" r:id="rId356" tooltip="https://images-na.ssl-images-amazon.com/images/I/71SXkH+kJRL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId357" tooltip="https://www.amazon.com/dp/B0HBQJ9M76"/>
-    <hyperlink ref="M48" r:id="rId358" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N48" r:id="rId359"/>
-    <hyperlink ref="AW48" r:id="rId360" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SWRS4GCWE28K"/>
-    <hyperlink ref="C49" r:id="rId361" tooltip="https://www.amazon.com/dp/B07BRVNXZW"/>
-    <hyperlink ref="G49" r:id="rId362" tooltip="https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B07BRVNXZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId363" tooltip="https://www.amazon.com/dp/B07BRVNXZW?psc=1"/>
-    <hyperlink ref="K49" r:id="rId364" tooltip="https://m.media-amazon.com/images/I/21Oz8FY385L._SX600_SY600_CR,0,0,600,600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId365" tooltip="https://www.amazon.com/dp/B07BRVNXZW"/>
-    <hyperlink ref="M49" r:id="rId366" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N49" r:id="rId367"/>
-    <hyperlink ref="AW49" r:id="rId368" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH"/>
-    <hyperlink ref="C50" r:id="rId369" tooltip="https://www.amazon.com/dp/B0GQ2W9M3M"/>
-    <hyperlink ref="G50" r:id="rId370" tooltip="https://www.amazon.com/stores/XIEBroRobotVacuumandMop/page/63D629A5-9469-4862-85F6-A208E9F2C951?lp_asin=B0GQ2W9M3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J50" r:id="rId371" tooltip="https://www.amazon.com/dp/B0GQ2W9M3M?psc=1"/>
-    <hyperlink ref="K50" r:id="rId372" tooltip="https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId373" tooltip="https://www.amazon.com/dp/B0GQ2W9M3M"/>
-    <hyperlink ref="M50" r:id="rId374" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N50" r:id="rId375"/>
-    <hyperlink ref="AW50" r:id="rId376" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P2R2P57KGCPN"/>
-    <hyperlink ref="C51" r:id="rId377" tooltip="https://www.amazon.com/dp/B0HFJJ589K"/>
-    <hyperlink ref="G51" r:id="rId378" tooltip="https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0HFJJ589K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J51" r:id="rId379" tooltip="https://www.amazon.com/dp/B0HFJJ589K?psc=1"/>
-    <hyperlink ref="K51" r:id="rId380" tooltip="https://images-na.ssl-images-amazon.com/images/I/71cb8CCFNBL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId381" tooltip="https://www.amazon.com/dp/B0HFJJ589K"/>
-    <hyperlink ref="M51" r:id="rId382" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N51" r:id="rId383"/>
-    <hyperlink ref="AW51" r:id="rId384" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18INPDUBKKX96"/>
+    <hyperlink ref="AW47" r:id="rId353" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH"/>
+    <hyperlink ref="C48" r:id="rId354" tooltip="https://www.amazon.com/dp/B0GQ2W9M3M"/>
+    <hyperlink ref="G48" r:id="rId355" tooltip="https://www.amazon.com/stores/XIEBroRobotVacuumandMop/page/63D629A5-9469-4862-85F6-A208E9F2C951?lp_asin=B0GQ2W9M3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J48" r:id="rId356" tooltip="https://www.amazon.com/dp/B0GQ2W9M3M?psc=1"/>
+    <hyperlink ref="K48" r:id="rId357" tooltip="https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId358" tooltip="https://www.amazon.com/dp/B0GQ2W9M3M"/>
+    <hyperlink ref="M48" r:id="rId359" tooltip="https://www.amazon.com/b?node=3743561"/>
+    <hyperlink ref="N48" r:id="rId360"/>
+    <hyperlink ref="AW48" r:id="rId361" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P2R2P57KGCPN"/>
+    <hyperlink ref="C49" r:id="rId362" tooltip="https://www.amazon.com/dp/B0HFJJ589K"/>
+    <hyperlink ref="G49" r:id="rId363" tooltip="https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0HFJJ589K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J49" r:id="rId364" tooltip="https://www.amazon.com/dp/B0HFJJ589K?psc=1"/>
+    <hyperlink ref="K49" r:id="rId365" tooltip="https://images-na.ssl-images-amazon.com/images/I/71cb8CCFNBL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId366" tooltip="https://www.amazon.com/dp/B0HFJJ589K"/>
+    <hyperlink ref="M49" r:id="rId367" tooltip="https://www.amazon.com/b?node=3743561"/>
+    <hyperlink ref="N49" r:id="rId368"/>
+    <hyperlink ref="AW49" r:id="rId369" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18INPDUBKKX96"/>
   </hyperlinks>
-  <drawing r:id="rId385"/>
+  <drawing r:id="rId370"/>
 </worksheet>
 </file>
 
@@ -20330,7 +19761,7 @@
         <v>603.2962189262586</v>
       </c>
       <c r="G2" s="22">
-        <v>0.2173439273552781</v>
+        <v>0.22725762193674576</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20351,7 +19782,7 @@
         <v>406.80115870060007</v>
       </c>
       <c r="G3" s="22">
-        <v>0.17554597048808174</v>
+        <v>0.18355313755091576</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20372,7 +19803,7 @@
         <v>312.13200508017144</v>
       </c>
       <c r="G4" s="22">
-        <v>0.1143972758229285</v>
+        <v>0.1196152714083611</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20393,7 +19824,7 @@
         <v>551.7590768364762</v>
       </c>
       <c r="G5" s="22">
-        <v>0.0645266742338252</v>
+        <v>0.0674699252760608</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20403,18 +19834,18 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <v>14693</v>
+        <v>12151</v>
       </c>
       <c r="C6" s="15">
-        <v>3901889</v>
+        <v>3844719</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="20">
-        <v>265.561083509154</v>
+        <v>316.4117356596165</v>
       </c>
       <c r="G6" s="22">
-        <v>0.1334211123723042</v>
+        <v>0.11537110357858357</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20424,18 +19855,18 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <v>7201</v>
+        <v>4939</v>
       </c>
       <c r="C7" s="15">
-        <v>2236426</v>
+        <v>2179899</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="20">
-        <v>310.57158727954453</v>
+        <v>441.36444624417896</v>
       </c>
       <c r="G7" s="22">
-        <v>0.06538933030646991</v>
+        <v>0.046894731345125854</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20456,7 +19887,7 @@
         <v>135.42993339427974</v>
       </c>
       <c r="G8" s="22">
-        <v>0.06953007945516458</v>
+        <v>0.07270155049800135</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20477,7 +19908,7 @@
         <v>158.01003904071388</v>
       </c>
       <c r="G9" s="22">
-        <v>0.04884449489216799</v>
+        <v>0.05107243569658473</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20498,7 +19929,7 @@
         <v>399.0</v>
       </c>
       <c r="G10" s="22">
-        <v>0.017334846765039727</v>
+        <v>0.01812554001576134</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20519,7 +19950,7 @@
         <v>113.1685393258427</v>
       </c>
       <c r="G11" s="22">
-        <v>0.04525766174801362</v>
+        <v>0.04732199656288869</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20540,7 +19971,7 @@
         <v>99.98999629492404</v>
       </c>
       <c r="G12" s="22">
-        <v>0.024508513053348467</v>
+        <v>0.02562641828315341</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20561,7 +19992,7 @@
         <v>446.9905838041431</v>
       </c>
       <c r="G13" s="22">
-        <v>0.004821793416572078</v>
+        <v>0.005041729569601504</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20582,7 +20013,7 @@
         <v>299.98977505112475</v>
       </c>
       <c r="G14" s="22">
-        <v>0.004440408626560727</v>
+        <v>0.004642948699689521</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20603,7 +20034,7 @@
         <v>299.9895178197065</v>
       </c>
       <c r="G15" s="22">
-        <v>0.004331441543700341</v>
+        <v>0.004529011308286097</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20624,7 +20055,7 @@
         <v>239.18584070796462</v>
       </c>
       <c r="G16" s="22">
-        <v>0.004104426787741203</v>
+        <v>0.004291641742862297</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20645,7 +20076,7 @@
         <v>199.97979797979798</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0026969353007945517</v>
+        <v>0.0028199504372347396</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20666,7 +20097,7 @@
         <v>114.68846153846154</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0023609534619750284</v>
+        <v>0.0024686434804075163</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20687,7 +20118,7 @@
         <v>119.9920634920635</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0011441543700340523</v>
+        <v>0.00119634260973595</v>
       </c>
     </row>
   </sheetData>
@@ -20762,7 +20193,7 @@
         <v>603.2962189262586</v>
       </c>
       <c r="G2" s="22">
-        <v>0.2173439273552781</v>
+        <v>0.22725762193674576</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20772,18 +20203,18 @@
         </is>
       </c>
       <c r="B3" s="15">
-        <v>30843</v>
+        <v>28581</v>
       </c>
       <c r="C3" s="15">
-        <v>10967910</v>
+        <v>10911383</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="20">
-        <v>355.6045131796518</v>
+        <v>381.7705118785207</v>
       </c>
       <c r="G3" s="22">
-        <v>0.2800726447219069</v>
+        <v>0.27137038197510466</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20793,18 +20224,18 @@
         </is>
       </c>
       <c r="B4" s="15">
-        <v>14693</v>
+        <v>12151</v>
       </c>
       <c r="C4" s="15">
-        <v>3901889</v>
+        <v>3844719</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="20">
-        <v>265.561083509154</v>
+        <v>316.4117356596165</v>
       </c>
       <c r="G4" s="22">
-        <v>0.1334211123723042</v>
+        <v>0.11537110357858357</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20825,7 +20256,7 @@
         <v>699.1199220923762</v>
       </c>
       <c r="G5" s="22">
-        <v>0.03263564131668559</v>
+        <v>0.034124248725325435</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20846,7 +20277,7 @@
         <v>699.990099009901</v>
       </c>
       <c r="G6" s="22">
-        <v>0.022011350737797957</v>
+        <v>0.02301535306349161</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20867,7 +20298,7 @@
         <v>198.76408281174773</v>
       </c>
       <c r="G7" s="22">
-        <v>0.056581157775255395</v>
+        <v>0.05916199048622782</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20888,7 +20319,7 @@
         <v>135.42993339427974</v>
       </c>
       <c r="G8" s="22">
-        <v>0.06953007945516458</v>
+        <v>0.07270155049800135</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20909,7 +20340,7 @@
         <v>799.9896907216495</v>
       </c>
       <c r="G9" s="22">
-        <v>0.011450624290578887</v>
+        <v>0.011972920879976453</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20930,7 +20361,7 @@
         <v>158.01003904071388</v>
       </c>
       <c r="G10" s="22">
-        <v>0.04884449489216799</v>
+        <v>0.05107243569658473</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20951,7 +20382,7 @@
         <v>424.9901220220802</v>
       </c>
       <c r="G11" s="22">
-        <v>0.015627695800227014</v>
+        <v>0.016340520883774367</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20972,7 +20403,7 @@
         <v>113.1685393258427</v>
       </c>
       <c r="G12" s="22">
-        <v>0.04525766174801362</v>
+        <v>0.04732199656288869</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20993,7 +20424,7 @@
         <v>269.98986486486484</v>
       </c>
       <c r="G13" s="22">
-        <v>0.018814982973893304</v>
+        <v>0.019673189582324512</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21014,7 +20445,7 @@
         <v>99.98999629492404</v>
       </c>
       <c r="G14" s="22">
-        <v>0.024508513053348467</v>
+        <v>0.02562641828315341</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21035,7 +20466,7 @@
         <v>446.9905838041431</v>
       </c>
       <c r="G15" s="22">
-        <v>0.004821793416572078</v>
+        <v>0.005041729569601504</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21056,7 +20487,7 @@
         <v>299.98977505112475</v>
       </c>
       <c r="G16" s="22">
-        <v>0.004440408626560727</v>
+        <v>0.004642948699689521</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21077,7 +20508,7 @@
         <v>299.9895178197065</v>
       </c>
       <c r="G17" s="22">
-        <v>0.004331441543700341</v>
+        <v>0.004529011308286097</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21098,7 +20529,7 @@
         <v>239.0891089108911</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0036685584562996597</v>
+        <v>0.0038358921772486017</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21119,7 +20550,7 @@
         <v>199.97979797979798</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0026969353007945517</v>
+        <v>0.0028199504372347396</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21140,7 +20571,7 @@
         <v>114.68846153846154</v>
       </c>
       <c r="G20" s="22">
-        <v>0.0023609534619750284</v>
+        <v>0.0024686434804075163</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21161,7 +20592,7 @@
         <v>119.9920634920635</v>
       </c>
       <c r="G21" s="22">
-        <v>0.0011441543700340523</v>
+        <v>0.00119634260973595</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21182,7 +20613,7 @@
         <v>240.0</v>
       </c>
       <c r="G22" s="22">
-        <v>0.0004358683314415437</v>
+        <v>0.0004557495656136953</v>
       </c>
     </row>
   </sheetData>
